--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="94">
   <si>
     <t>Mat</t>
   </si>
@@ -85,34 +85,73 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>JACINTO</t>
+  </si>
+  <si>
+    <t>MAZABA</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>YEPEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>JACINTO</t>
-  </si>
-  <si>
-    <t>LEON</t>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>LOYO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>QUIAHUA</t>
@@ -121,52 +160,61 @@
     <t>RAMOS</t>
   </si>
   <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>MORALES</t>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>ISLAS</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MACUISTLE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>AVALOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
   </si>
   <si>
     <t>DE LA ROSA</t>
   </si>
   <si>
-    <t>MACUISTLE</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>JAIMES</t>
+  </si>
+  <si>
+    <t>AVILA</t>
   </si>
   <si>
     <t>PANZO</t>
@@ -175,76 +223,82 @@
     <t>JACOBO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>JAIMES</t>
-  </si>
-  <si>
     <t>JOHANAN</t>
   </si>
   <si>
-    <t>CRISTIAN YAIR</t>
+    <t>ALEXIS URIEL</t>
+  </si>
+  <si>
+    <t>VICTOR ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ESTRELLA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
+  </si>
+  <si>
+    <t>MYA YAMILET</t>
+  </si>
+  <si>
+    <t>VALERIA JUNUET</t>
+  </si>
+  <si>
+    <t>ALISON</t>
+  </si>
+  <si>
+    <t>NATHAN KARLO</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>CRISTOFER FRANCISCO</t>
+  </si>
+  <si>
+    <t>MATIAS</t>
+  </si>
+  <si>
+    <t>MANUEL ABDUL</t>
+  </si>
+  <si>
+    <t>JOANNA JAQUELINE</t>
+  </si>
+  <si>
+    <t>CRISTHIAN GAEL</t>
+  </si>
+  <si>
+    <t>LUIS ALFREDO</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>JOY JARA</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
   </si>
   <si>
     <t>INGRID ABIGAIL</t>
   </si>
   <si>
-    <t>ANGEL FRANCISCO</t>
-  </si>
-  <si>
-    <t>CALEB SANTIAGO</t>
-  </si>
-  <si>
-    <t>MYA YAMILET</t>
-  </si>
-  <si>
     <t>MARIA KAREN</t>
   </si>
   <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ALISON</t>
-  </si>
-  <si>
-    <t>NAARA SAFIR</t>
-  </si>
-  <si>
-    <t>MATIAS</t>
-  </si>
-  <si>
-    <t>CRISTHIAN GAEL</t>
+    <t>KAREN ITAMAR</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>JESUS ALAYN</t>
   </si>
   <si>
     <t>JONATHAN MICHEL</t>
   </si>
   <si>
     <t>DIEGO JOSUE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>ALEXIS URIEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>NATHAN KARLO</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
   </si>
 </sst>
 </file>
@@ -886,16 +940,19 @@
         <v>48</v>
       </c>
       <c r="D4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>79.17</v>
+      </c>
+      <c r="H4">
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1072,16 +1129,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G4">
-        <v>70.83</v>
+        <v>79.17</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1169,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1207,10 +1264,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1224,22 +1281,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920071</v>
+        <v>24330051920137</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1247,22 +1304,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920352</v>
+        <v>24330051920334</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1270,16 +1327,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920347</v>
+        <v>24330051920250</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1293,16 +1350,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920351</v>
+        <v>24330051920347</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1319,13 +1376,13 @@
         <v>24330051920117</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1339,16 +1396,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920086</v>
+        <v>24330051920349</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1362,22 +1419,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920115</v>
+        <v>24330051920160</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1385,16 +1442,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920160</v>
+        <v>24330051920216</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1408,16 +1465,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920162</v>
+        <v>24330051920359</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1431,22 +1488,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920049</v>
+        <v>24330051920163</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1454,22 +1511,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920271</v>
+        <v>24330051920049</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1477,22 +1534,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920371</v>
+        <v>24330051920373</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1500,16 +1557,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920385</v>
+        <v>24330051920382</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1523,16 +1580,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920381</v>
+        <v>24330051920271</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1546,68 +1603,68 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920137</v>
+        <v>24330051920312</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920350</v>
+        <v>24330051920381</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920216</v>
+        <v>24330051920353</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1615,24 +1672,185 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
+        <v>24330051920350</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920352</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920086</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920195</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
         <v>24330051920366</v>
       </c>
-      <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
         <v>13</v>
       </c>
-      <c r="G20">
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920364</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24330051920371</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>24330051920385</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="75">
   <si>
     <t>Mat</t>
   </si>
@@ -82,162 +82,114 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>JACINTO</t>
+  </si>
+  <si>
+    <t>MAZABA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>YEPEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ISLAS</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>JACINTO</t>
-  </si>
-  <si>
-    <t>MAZABA</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>LEON</t>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>LOYO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>ISLAS</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MACUISTLE</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>AVALOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
     <t>MARIA</t>
   </si>
   <si>
-    <t>JAIMES</t>
+    <t>MOCTEZUMA</t>
   </si>
   <si>
     <t>AVILA</t>
   </si>
   <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
-    <t>JOHANAN</t>
-  </si>
-  <si>
-    <t>ALEXIS URIEL</t>
-  </si>
-  <si>
     <t>VICTOR ALEJANDRO</t>
   </si>
   <si>
-    <t>ESTRELLA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
-  </si>
-  <si>
     <t>MYA YAMILET</t>
   </si>
   <si>
@@ -247,9 +199,6 @@
     <t>ALISON</t>
   </si>
   <si>
-    <t>NATHAN KARLO</t>
-  </si>
-  <si>
     <t>JAZMIN</t>
   </si>
   <si>
@@ -262,15 +211,15 @@
     <t>MANUEL ABDUL</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>JOANNA JAQUELINE</t>
   </si>
   <si>
     <t>CRISTHIAN GAEL</t>
   </si>
   <si>
-    <t>LUIS ALFREDO</t>
-  </si>
-  <si>
     <t>YAEL</t>
   </si>
   <si>
@@ -289,16 +238,10 @@
     <t>KAREN ITAMAR</t>
   </si>
   <si>
-    <t>EVELYN</t>
+    <t>ZURY DALAY</t>
   </si>
   <si>
     <t>JESUS ALAYN</t>
-  </si>
-  <si>
-    <t>JONATHAN MICHEL</t>
-  </si>
-  <si>
-    <t>DIEGO JOSUE</t>
   </si>
 </sst>
 </file>
@@ -894,16 +837,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>82.5</v>
+      </c>
+      <c r="H2">
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -917,16 +863,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75.61</v>
+      </c>
+      <c r="H3">
+        <v>5.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -966,16 +915,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>80.56</v>
+      </c>
+      <c r="H5">
+        <v>6.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -989,16 +941,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>72.97</v>
+      </c>
+      <c r="H6">
+        <v>6.2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1012,16 +967,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>78.79000000000001</v>
+      </c>
+      <c r="H7">
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -1077,16 +1035,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>77.5</v>
+        <v>82.5</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1103,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>70.73</v>
+        <v>75.61</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1164,7 +1122,7 @@
         <v>80.56</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1181,16 +1139,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>75.68000000000001</v>
+        <v>72.97</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1207,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>69.7</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1226,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1258,22 +1216,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920141</v>
+        <v>24330051920334</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1281,22 +1239,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920137</v>
+        <v>24330051920117</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1304,22 +1262,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920334</v>
+        <v>24330051920349</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1327,22 +1285,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920250</v>
+        <v>24330051920160</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1350,22 +1308,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920347</v>
+        <v>24330051920359</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1373,22 +1331,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920117</v>
+        <v>24330051920163</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1396,22 +1354,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920349</v>
+        <v>24330051920049</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1419,22 +1377,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920160</v>
+        <v>24330051920373</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1442,22 +1400,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920216</v>
+        <v>24330051920052</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1465,22 +1423,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920359</v>
+        <v>24330051920382</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1488,22 +1446,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920163</v>
+        <v>24330051920271</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1511,22 +1469,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920049</v>
+        <v>24330051920381</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1534,137 +1492,137 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920373</v>
+        <v>24330051920353</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920382</v>
+        <v>24330051920350</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920271</v>
+        <v>24330051920352</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920312</v>
+        <v>24330051920086</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920381</v>
+        <v>24330051920195</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920353</v>
+        <v>24330051920367</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1672,185 +1630,24 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920350</v>
+        <v>24330051920364</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920352</v>
-      </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" t="s">
-        <v>87</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920086</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>24330051920195</v>
-      </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>24330051920366</v>
-      </c>
-      <c r="B24" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>24330051920364</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" t="s">
-        <v>91</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>24330051920371</v>
-      </c>
-      <c r="B26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>24330051920385</v>
-      </c>
-      <c r="B27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
   <si>
     <t>Mat</t>
   </si>
@@ -82,45 +82,45 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>JACINTO</t>
+  </si>
+  <si>
+    <t>MAZABA</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>YEPEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>JACINTO</t>
-  </si>
-  <si>
-    <t>MAZABA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -139,36 +139,36 @@
     <t>MORALES</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ISLAS</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>LOBATO</t>
   </si>
   <si>
@@ -187,43 +187,49 @@
     <t>AVILA</t>
   </si>
   <si>
+    <t>VERONICA ITZEL</t>
+  </si>
+  <si>
+    <t>CRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>MYA YAMILET</t>
+  </si>
+  <si>
+    <t>VALERIA JUNUET</t>
+  </si>
+  <si>
+    <t>ALISON</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>CRISTOFER FRANCISCO</t>
+  </si>
+  <si>
+    <t>MATIAS</t>
+  </si>
+  <si>
+    <t>MANUEL ABDUL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JOANNA JAQUELINE</t>
+  </si>
+  <si>
+    <t>CRISTHIAN GAEL</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>JOY JARA</t>
+  </si>
+  <si>
     <t>VICTOR ALEJANDRO</t>
-  </si>
-  <si>
-    <t>MYA YAMILET</t>
-  </si>
-  <si>
-    <t>VALERIA JUNUET</t>
-  </si>
-  <si>
-    <t>ALISON</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>CRISTOFER FRANCISCO</t>
-  </si>
-  <si>
-    <t>MATIAS</t>
-  </si>
-  <si>
-    <t>MANUEL ABDUL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>JOANNA JAQUELINE</t>
-  </si>
-  <si>
-    <t>CRISTHIAN GAEL</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>JOY JARA</t>
   </si>
   <si>
     <t>MARIANA</t>
@@ -1184,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1216,13 +1222,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920334</v>
+        <v>24330051920336</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -1239,13 +1245,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920117</v>
+        <v>24330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>57</v>
@@ -1254,7 +1260,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1262,13 +1268,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920349</v>
+        <v>24330051920117</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
         <v>58</v>
@@ -1285,13 +1291,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920160</v>
+        <v>24330051920349</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
         <v>59</v>
@@ -1300,7 +1306,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1308,13 +1314,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920359</v>
+        <v>24330051920160</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
         <v>60</v>
@@ -1331,13 +1337,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920163</v>
+        <v>24330051920359</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
         <v>61</v>
@@ -1354,13 +1360,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920049</v>
+        <v>24330051920163</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
         <v>62</v>
@@ -1369,7 +1375,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1377,13 +1383,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920373</v>
+        <v>24330051920049</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
         <v>63</v>
@@ -1400,13 +1406,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920052</v>
+        <v>24330051920373</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
         <v>64</v>
@@ -1423,13 +1429,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920382</v>
+        <v>24330051920052</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>65</v>
@@ -1438,7 +1444,7 @@
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1446,13 +1452,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920271</v>
+        <v>24330051920382</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
         <v>66</v>
@@ -1469,13 +1475,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920381</v>
+        <v>24330051920271</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
         <v>67</v>
@@ -1492,13 +1498,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920353</v>
+        <v>24330051920381</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
         <v>68</v>
@@ -1507,21 +1513,21 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920350</v>
+        <v>24330051920353</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
         <v>69</v>
@@ -1530,7 +1536,7 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1538,13 +1544,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920352</v>
+        <v>24330051920334</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
         <v>70</v>
@@ -1553,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1561,13 +1567,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920086</v>
+        <v>24330051920350</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
@@ -1584,13 +1590,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920195</v>
+        <v>24330051920352</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
         <v>72</v>
@@ -1599,7 +1605,7 @@
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1607,13 +1613,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920367</v>
+        <v>24330051920086</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
         <v>73</v>
@@ -1622,7 +1628,7 @@
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1630,13 +1636,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920364</v>
+        <v>24330051920195</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
         <v>74</v>
@@ -1645,9 +1651,55 @@
         <v>8</v>
       </c>
       <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920367</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920364</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
         <v>13</v>
       </c>
-      <c r="G20">
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -85,12 +85,15 @@
     <t>CORTES</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -133,12 +136,12 @@
     <t>ANGEL</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
@@ -190,46 +193,49 @@
     <t>VERONICA ITZEL</t>
   </si>
   <si>
+    <t>ANGEL ALBERTO</t>
+  </si>
+  <si>
+    <t>MYA YAMILET</t>
+  </si>
+  <si>
+    <t>VALERIA JUNUET</t>
+  </si>
+  <si>
+    <t>ALISON</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>CRISTOFER FRANCISCO</t>
+  </si>
+  <si>
+    <t>MATIAS</t>
+  </si>
+  <si>
+    <t>MANUEL ABDUL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>JOANNA JAQUELINE</t>
+  </si>
+  <si>
+    <t>CRISTHIAN GAEL</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>JOY JARA</t>
+  </si>
+  <si>
+    <t>VICTOR ALEJANDRO</t>
+  </si>
+  <si>
     <t>CRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>MYA YAMILET</t>
-  </si>
-  <si>
-    <t>VALERIA JUNUET</t>
-  </si>
-  <si>
-    <t>ALISON</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>CRISTOFER FRANCISCO</t>
-  </si>
-  <si>
-    <t>MATIAS</t>
-  </si>
-  <si>
-    <t>MANUEL ABDUL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>JOANNA JAQUELINE</t>
-  </si>
-  <si>
-    <t>CRISTHIAN GAEL</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>JOY JARA</t>
-  </si>
-  <si>
-    <t>VICTOR ALEJANDRO</t>
   </si>
   <si>
     <t>MARIANA</t>
@@ -1190,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1228,10 +1234,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1245,16 +1251,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920071</v>
+        <v>24330051920340</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1274,10 +1280,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1294,13 +1300,13 @@
         <v>24330051920349</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1320,10 +1326,10 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1340,13 +1346,13 @@
         <v>24330051920359</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1363,13 +1369,13 @@
         <v>24330051920163</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1386,13 +1392,13 @@
         <v>24330051920049</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1409,13 +1415,13 @@
         <v>24330051920373</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1432,13 +1438,13 @@
         <v>24330051920052</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1455,13 +1461,13 @@
         <v>24330051920382</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1478,13 +1484,13 @@
         <v>24330051920271</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1501,13 +1507,13 @@
         <v>24330051920381</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1524,13 +1530,13 @@
         <v>24330051920353</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1547,13 +1553,13 @@
         <v>24330051920334</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1567,22 +1573,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920350</v>
+        <v>24330051920071</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1590,7 +1596,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920352</v>
+        <v>24330051920350</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
@@ -1599,7 +1605,7 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1613,7 +1619,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920086</v>
+        <v>24330051920352</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
@@ -1622,7 +1628,7 @@
         <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1636,7 +1642,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920195</v>
+        <v>24330051920086</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
@@ -1645,13 +1651,13 @@
         <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1659,7 +1665,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920367</v>
+        <v>24330051920195</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
@@ -1668,7 +1674,7 @@
         <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1682,24 +1688,47 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920364</v>
+        <v>24330051920367</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
         <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920364</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
         <v>13</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="104">
   <si>
     <t>Mat</t>
   </si>
@@ -82,12 +82,42 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>PLIEGO</t>
   </si>
   <si>
@@ -139,7 +169,28 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>OROZCO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MACUISTLE</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>TORRES</t>
@@ -157,9 +208,6 @@
     <t>QUINTERO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -178,9 +226,6 @@
     <t>DE LA ROSA</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>MARIA</t>
   </si>
   <si>
@@ -188,6 +233,36 @@
   </si>
   <si>
     <t>AVILA</t>
+  </si>
+  <si>
+    <t>ANGEL ALEXANDER</t>
+  </si>
+  <si>
+    <t>SARA ALY</t>
+  </si>
+  <si>
+    <t>DIANA CAMILA</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>JESUS ANDRES</t>
+  </si>
+  <si>
+    <t>ESTRELLA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
+  </si>
+  <si>
+    <t>DAMARIZ</t>
+  </si>
+  <si>
+    <t>ANDY ARELY</t>
   </si>
   <si>
     <t>VERONICA ITZEL</t>
@@ -1196,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1228,223 +1303,223 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920336</v>
+        <v>24330051920328</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920340</v>
+        <v>24330051920326</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920117</v>
+        <v>24330051920040</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920349</v>
+        <v>24330051920038</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920160</v>
+        <v>24330051920233</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920359</v>
+        <v>24330051920338</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920163</v>
+        <v>24330051920065</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920049</v>
+        <v>24330051920250</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920373</v>
+        <v>24330051920347</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920052</v>
+        <v>23330051920341</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1453,21 +1528,21 @@
         <v>13</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920382</v>
+        <v>24330051920028</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1476,27 +1551,27 @@
         <v>14</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920271</v>
+        <v>24330051920336</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1504,22 +1579,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920381</v>
+        <v>24330051920340</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1527,208 +1602,461 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920353</v>
+        <v>24330051920117</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920334</v>
+        <v>24330051920349</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920071</v>
+        <v>24330051920160</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920350</v>
+        <v>24330051920359</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920352</v>
+        <v>24330051920163</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920086</v>
+        <v>24330051920049</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920195</v>
+        <v>24330051920373</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920367</v>
+        <v>24330051920052</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
+        <v>24330051920382</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>24330051920271</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920381</v>
+      </c>
+      <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24330051920353</v>
+      </c>
+      <c r="B26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>24330051920334</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>24330051920071</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>24330051920350</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>24330051920352</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>24330051920086</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>24330051920195</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>24330051920367</v>
+      </c>
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
         <v>24330051920364</v>
       </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="B34" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
         <v>13</v>
       </c>
-      <c r="G23">
+      <c r="G34">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="125">
   <si>
     <t>Mat</t>
   </si>
@@ -85,250 +85,313 @@
     <t>CID</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>PARADA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>MACHORRO</t>
   </si>
   <si>
+    <t>RAZCON</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>JACINTO</t>
+  </si>
+  <si>
     <t>MOTA</t>
   </si>
   <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
+    <t>CALIHUA</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>JACINTO</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
   </si>
   <si>
     <t>MAZABA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
     <t>YEPEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>OROZCO</t>
   </si>
   <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>MACUISTLE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>MACUISTLE</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ISLAS</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>MOCTEZUMA</t>
   </si>
   <si>
     <t>QUINTERO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>AVILA</t>
   </si>
   <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ISLAS</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>AVILA</t>
-  </si>
-  <si>
     <t>ANGEL ALEXANDER</t>
   </si>
   <si>
+    <t>AXEL BENITO</t>
+  </si>
+  <si>
+    <t>YERIEL</t>
+  </si>
+  <si>
+    <t>MARCO DIDIEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>NAARA SAFIR</t>
+  </si>
+  <si>
+    <t>ANGEL GAEL</t>
+  </si>
+  <si>
+    <t>YOSHUA RAFAEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>JOSE ARTURO</t>
+  </si>
+  <si>
+    <t>ESTRELLA MONTSERRAT</t>
+  </si>
+  <si>
+    <t>ANGEL FRANCISCO</t>
+  </si>
+  <si>
     <t>SARA ALY</t>
   </si>
   <si>
+    <t>VERONICA ITZEL</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>JESUS ANDRES</t>
+  </si>
+  <si>
+    <t>MYA YAMILET</t>
+  </si>
+  <si>
+    <t>VALERIA JUNUET</t>
+  </si>
+  <si>
+    <t>ALISON</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>CRISTOFER FRANCISCO</t>
+  </si>
+  <si>
+    <t>DAMARIZ</t>
+  </si>
+  <si>
+    <t>MATIAS</t>
+  </si>
+  <si>
     <t>DIANA CAMILA</t>
   </si>
   <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>JESUS ANDRES</t>
-  </si>
-  <si>
-    <t>ESTRELLA MONTSERRAT</t>
-  </si>
-  <si>
-    <t>ANGEL FRANCISCO</t>
-  </si>
-  <si>
-    <t>DAMARIZ</t>
+    <t>JOANNA JAQUELINE</t>
   </si>
   <si>
     <t>ANDY ARELY</t>
   </si>
   <si>
-    <t>VERONICA ITZEL</t>
+    <t>JOY JARA</t>
   </si>
   <si>
     <t>ANGEL ALBERTO</t>
   </si>
   <si>
-    <t>MYA YAMILET</t>
-  </si>
-  <si>
-    <t>VALERIA JUNUET</t>
-  </si>
-  <si>
-    <t>ALISON</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>CRISTOFER FRANCISCO</t>
-  </si>
-  <si>
-    <t>MATIAS</t>
+    <t>VICTOR ALEJANDRO</t>
+  </si>
+  <si>
+    <t>CRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>INGRID ABIGAIL</t>
+  </si>
+  <si>
+    <t>MARIA KAREN</t>
+  </si>
+  <si>
+    <t>KAREN ITAMAR</t>
+  </si>
+  <si>
+    <t>ZURY DALAY</t>
   </si>
   <si>
     <t>MANUEL ABDUL</t>
   </si>
   <si>
+    <t>JESUS ALAYN</t>
+  </si>
+  <si>
     <t>MARIA FERNANDA</t>
   </si>
   <si>
-    <t>JOANNA JAQUELINE</t>
-  </si>
-  <si>
     <t>CRISTHIAN GAEL</t>
   </si>
   <si>
     <t>YAEL</t>
-  </si>
-  <si>
-    <t>JOY JARA</t>
-  </si>
-  <si>
-    <t>VICTOR ALEJANDRO</t>
-  </si>
-  <si>
-    <t>CRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>INGRID ABIGAIL</t>
-  </si>
-  <si>
-    <t>MARIA KAREN</t>
-  </si>
-  <si>
-    <t>KAREN ITAMAR</t>
-  </si>
-  <si>
-    <t>ZURY DALAY</t>
-  </si>
-  <si>
-    <t>JESUS ALAYN</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1309,10 +1372,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1326,16 +1389,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920326</v>
+        <v>24330051920329</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1349,22 +1412,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920040</v>
+        <v>24330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1372,22 +1435,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920038</v>
+        <v>24330051920404</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1395,114 +1458,114 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920233</v>
+        <v>24330051920348</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920338</v>
+        <v>24330051920162</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920065</v>
+        <v>24330051920375</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920250</v>
+        <v>24330051920259</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920347</v>
+        <v>24330051920233</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -1510,22 +1573,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920341</v>
+        <v>24330051920326</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -1533,22 +1596,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920028</v>
+        <v>24330051920307</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -1556,91 +1619,91 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920336</v>
+        <v>24330051920250</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920340</v>
+        <v>24330051920347</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920117</v>
+        <v>24330051920040</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920349</v>
+        <v>24330051920336</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1648,22 +1711,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920160</v>
+        <v>24330051920338</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1671,22 +1734,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920359</v>
+        <v>24330051920065</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1694,22 +1757,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920163</v>
+        <v>24330051920117</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G19">
         <v>2</v>
@@ -1717,22 +1780,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920049</v>
+        <v>24330051920349</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1740,22 +1803,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920373</v>
+        <v>24330051920160</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>2</v>
@@ -1763,22 +1826,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920052</v>
+        <v>24330051920359</v>
       </c>
       <c r="B22" t="s">
         <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -1786,22 +1849,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920382</v>
+        <v>24330051920163</v>
       </c>
       <c r="B23" t="s">
         <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1809,22 +1872,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>24330051920271</v>
+        <v>23330051920341</v>
       </c>
       <c r="B24" t="s">
         <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -1832,22 +1895,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920381</v>
+        <v>24330051920049</v>
       </c>
       <c r="B25" t="s">
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1855,91 +1918,91 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920353</v>
+        <v>24330051920038</v>
       </c>
       <c r="B26" t="s">
         <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920334</v>
+        <v>24330051920382</v>
       </c>
       <c r="B27" t="s">
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920071</v>
+        <v>24330051920028</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920350</v>
+        <v>24330051920353</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1947,22 +2010,22 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920352</v>
+        <v>24330051920340</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1970,22 +2033,22 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920086</v>
+        <v>24330051920334</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D31" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1993,22 +2056,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>24330051920195</v>
+        <v>24330051920071</v>
       </c>
       <c r="B32" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2016,22 +2079,22 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>24330051920367</v>
+        <v>24330051920350</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2039,24 +2102,208 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>24330051920364</v>
+        <v>24330051920352</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>24330051920086</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>24330051920195</v>
+      </c>
+      <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>24330051920367</v>
+      </c>
+      <c r="B37" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>24330051920373</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
         <v>13</v>
       </c>
-      <c r="G34">
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>24330051920364</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>24330051920052</v>
+      </c>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" t="s">
+        <v>122</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>24330051920271</v>
+      </c>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>123</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>24330051920381</v>
+      </c>
+      <c r="B42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D42" t="s">
+        <v>124</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
+++ b/docentes/Herrera Serrano Mayra Iliana - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="130">
   <si>
     <t>Mat</t>
   </si>
@@ -82,37 +82,52 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>CID</t>
   </si>
   <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>RAZCON</t>
+  </si>
+  <si>
+    <t>PARADA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>PARADA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>RAZCON</t>
+    <t>TIZA</t>
   </si>
   <si>
     <t>ESTEVEZ</t>
@@ -121,100 +136,97 @@
     <t>MOLINA</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>CORTES</t>
   </si>
   <si>
-    <t>TIZA</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>JACINTO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
   </si>
   <si>
     <t>PLIEGO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>JACINTO</t>
-  </si>
-  <si>
-    <t>MOTA</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>MAZABA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
   </si>
   <si>
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>MAZABA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
     <t>YEPEZ</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>OROZCO</t>
   </si>
   <si>
-    <t>RANGEL</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>MORA</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
   </si>
   <si>
     <t>PELLICO</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>VERA</t>
   </si>
   <si>
     <t>MARIN</t>
@@ -223,7 +235,28 @@
     <t>MACUISTLE</t>
   </si>
   <si>
-    <t>VERA</t>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ISLAS</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
   </si>
   <si>
     <t>TORRES</t>
@@ -232,76 +265,67 @@
     <t>RICO</t>
   </si>
   <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>AVILA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ISLAS</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>AVILA</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
+    <t>YERIEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>NAARA SAFIR</t>
+  </si>
+  <si>
+    <t>ANGEL GAEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
     <t>ANGEL ALEXANDER</t>
   </si>
   <si>
-    <t>AXEL BENITO</t>
-  </si>
-  <si>
-    <t>YERIEL</t>
+    <t>JOSE ARTURO</t>
   </si>
   <si>
     <t>MARCO DIDIEL</t>
   </si>
   <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>NAARA SAFIR</t>
-  </si>
-  <si>
-    <t>ANGEL GAEL</t>
+    <t>ULISES EZEQUIEL</t>
+  </si>
+  <si>
+    <t>CAROLINA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SARA ALY</t>
+  </si>
+  <si>
+    <t>NESTOR NOE</t>
   </si>
   <si>
     <t>YOSHUA RAFAEL</t>
   </si>
   <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>JOSE ARTURO</t>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>JESUS ANDRES</t>
   </si>
   <si>
     <t>ESTRELLA MONTSERRAT</t>
@@ -310,82 +334,73 @@
     <t>ANGEL FRANCISCO</t>
   </si>
   <si>
-    <t>SARA ALY</t>
+    <t>ALISON</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>CRISTOFER FRANCISCO</t>
+  </si>
+  <si>
+    <t>DAMARIZ</t>
+  </si>
+  <si>
+    <t>MATIAS</t>
+  </si>
+  <si>
+    <t>DIANA CAMILA</t>
+  </si>
+  <si>
+    <t>ANDY ARELY</t>
+  </si>
+  <si>
+    <t>JOY JARA</t>
   </si>
   <si>
     <t>VERONICA ITZEL</t>
   </si>
   <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>JESUS ANDRES</t>
+    <t>ANGEL ALBERTO</t>
+  </si>
+  <si>
+    <t>VICTOR ALEJANDRO</t>
+  </si>
+  <si>
+    <t>CRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>INGRID ABIGAIL</t>
   </si>
   <si>
     <t>MYA YAMILET</t>
   </si>
   <si>
+    <t>MARIA KAREN</t>
+  </si>
+  <si>
     <t>VALERIA JUNUET</t>
   </si>
   <si>
-    <t>ALISON</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>CRISTOFER FRANCISCO</t>
-  </si>
-  <si>
-    <t>DAMARIZ</t>
-  </si>
-  <si>
-    <t>MATIAS</t>
-  </si>
-  <si>
-    <t>DIANA CAMILA</t>
+    <t>KAREN ITAMAR</t>
+  </si>
+  <si>
+    <t>ZURY DALAY</t>
+  </si>
+  <si>
+    <t>MANUEL ABDUL</t>
+  </si>
+  <si>
+    <t>JESUS ALAYN</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>JOANNA JAQUELINE</t>
-  </si>
-  <si>
-    <t>ANDY ARELY</t>
-  </si>
-  <si>
-    <t>JOY JARA</t>
-  </si>
-  <si>
-    <t>ANGEL ALBERTO</t>
-  </si>
-  <si>
-    <t>VICTOR ALEJANDRO</t>
-  </si>
-  <si>
-    <t>CRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>INGRID ABIGAIL</t>
-  </si>
-  <si>
-    <t>MARIA KAREN</t>
-  </si>
-  <si>
-    <t>KAREN ITAMAR</t>
-  </si>
-  <si>
-    <t>ZURY DALAY</t>
-  </si>
-  <si>
-    <t>MANUEL ABDUL</t>
-  </si>
-  <si>
-    <t>JESUS ALAYN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>CRISTHIAN GAEL</t>
@@ -1334,7 +1349,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1366,16 +1381,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920328</v>
+        <v>24330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1389,22 +1404,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920329</v>
+        <v>24330051920348</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1412,22 +1427,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920145</v>
+        <v>24330051920162</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>4</v>
@@ -1435,22 +1450,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920404</v>
+        <v>24330051920375</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>4</v>
@@ -1458,114 +1473,114 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920348</v>
+        <v>24330051920233</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920162</v>
+        <v>24330051920328</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920375</v>
+        <v>24330051920326</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920259</v>
+        <v>24330051920307</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920233</v>
+        <v>24330051920404</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -1573,22 +1588,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920326</v>
+        <v>24330051920169</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>3</v>
@@ -1596,22 +1611,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920307</v>
+        <v>24330051920139</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>3</v>
@@ -1619,22 +1634,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920250</v>
+        <v>24330051920040</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>3</v>
@@ -1642,7 +1657,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920347</v>
+        <v>24330051920009</v>
       </c>
       <c r="B14" t="s">
         <v>33</v>
@@ -1651,13 +1666,13 @@
         <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -1665,22 +1680,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920040</v>
+        <v>24330051920259</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -1688,16 +1703,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920336</v>
+        <v>24330051920338</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1711,16 +1726,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920338</v>
+        <v>24330051920065</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1734,22 +1749,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920065</v>
+        <v>24330051920250</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1757,16 +1772,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920117</v>
+        <v>24330051920347</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1780,22 +1795,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920349</v>
+        <v>24330051920160</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>2</v>
@@ -1803,16 +1818,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920160</v>
+        <v>24330051920359</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1826,16 +1841,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920359</v>
+        <v>24330051920163</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1849,22 +1864,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920163</v>
+        <v>23330051920341</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23">
         <v>2</v>
@@ -1872,16 +1887,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920341</v>
+        <v>24330051920049</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1895,16 +1910,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>24330051920049</v>
+        <v>24330051920038</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1918,22 +1933,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>24330051920038</v>
+        <v>24330051920028</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1941,68 +1956,68 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24330051920382</v>
+        <v>24330051920353</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>24330051920028</v>
+        <v>24330051920336</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
         <v>48</v>
       </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24330051920353</v>
+        <v>24330051920340</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2010,16 +2025,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24330051920340</v>
+        <v>24330051920334</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2033,16 +2048,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>24330051920334</v>
+        <v>24330051920071</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2056,22 +2071,22 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>24330051920071</v>
+        <v>24330051920350</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2079,16 +2094,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>24330051920350</v>
+        <v>24330051920352</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2102,16 +2117,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>24330051920352</v>
+        <v>24330051920117</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2128,13 +2143,13 @@
         <v>24330051920086</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2148,22 +2163,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>24330051920195</v>
+        <v>24330051920349</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2171,16 +2186,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>24330051920367</v>
+        <v>24330051920195</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2194,22 +2209,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>24330051920373</v>
+        <v>24330051920367</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2217,16 +2232,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>24330051920364</v>
+        <v>24330051920373</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D39" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2240,16 +2255,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>24330051920052</v>
+        <v>24330051920364</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2263,22 +2278,22 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>24330051920271</v>
+        <v>24330051920052</v>
       </c>
       <c r="B41" t="s">
         <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2286,16 +2301,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>24330051920381</v>
+        <v>24330051920382</v>
       </c>
       <c r="B42" t="s">
         <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2304,6 +2319,52 @@
         <v>14</v>
       </c>
       <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>24330051920271</v>
+      </c>
+      <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" t="s">
+        <v>128</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>24330051920381</v>
+      </c>
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>129</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44">
         <v>1</v>
       </c>
     </row>
